--- a/hoon/120겹파이 프챠 레시피 260619.xlsx
+++ b/hoon/120겹파이 프챠 레시피 260619.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\anti-gv\25. 120pie(new)_2\hoon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E74AB24-AA56-4EC8-975F-6935EDB8D340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8EBF79-5E46-4670-99A9-F0CF4C231870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24615" yWindow="45" windowWidth="26715" windowHeight="20880" xr2:uid="{DB46F759-9111-45F6-9CB4-D022B1A69D76}"/>
+    <workbookView xWindow="4545" yWindow="270" windowWidth="17310" windowHeight="20880" xr2:uid="{DB46F759-9111-45F6-9CB4-D022B1A69D76}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
